--- a/app/reports/LSBA_research.xlsx
+++ b/app/reports/LSBA_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.0472</v>
+        <v>0.04719999790191651</v>
       </c>
     </row>
     <row r="6">
